--- a/hr_toolkit/templates/social_security_detail_template.xlsx
+++ b/hr_toolkit/templates/social_security_detail_template.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="14800"/>
+    <workbookView windowHeight="15040"/>
   </bookViews>
   <sheets>
     <sheet name="社保明细表模板" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="63">
   <si>
     <t>XXX公司2025年9月社保明细表</t>
   </si>
@@ -211,25 +211,48 @@
   </si>
   <si>
     <t>单位</t>
+  </si>
+  <si>
+    <t>春苗</t>
+  </si>
+  <si>
+    <t>南昌</t>
+  </si>
+  <si>
+    <t>上饶</t>
+  </si>
+  <si>
+    <t>张三</t>
+  </si>
+  <si>
+    <t>123456</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="4">
+  <numFmts count="6">
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="176" formatCode="0.0%"/>
+    <numFmt numFmtId="177" formatCode="0.00_ "/>
   </numFmts>
-  <fonts count="23">
+  <fonts count="25">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="134"/>
     </font>
     <font>
       <sz val="10"/>
@@ -250,6 +273,11 @@
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="宋体"/>
+      <charset val="134"/>
     </font>
     <font>
       <u/>
@@ -682,9 +710,7 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
+      <left/>
       <right/>
       <top style="thin">
         <color auto="1"/>
@@ -695,7 +721,9 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
       <right/>
       <top style="thin">
         <color auto="1"/>
@@ -847,286 +875,328 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="13" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="14" borderId="11" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="15" borderId="12" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="15" borderId="11" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="16" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="14" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="15" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="14" borderId="11" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="15" borderId="12" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="15" borderId="11" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="16" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="14" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="15" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="50">
+  <cellXfs count="64">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="10" fontId="5" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="5" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="10" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="11" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="10" fontId="5" fillId="0" borderId="2" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="11" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="5" fillId="9" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="11" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="11" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="12" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="11" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="12" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="12" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="11" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="12" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="12" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="12" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="12" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="12" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="43" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="43" fontId="3" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="5" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="4" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="43" fontId="4" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="43" fontId="5" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1180,7 +1250,14 @@
     <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
     <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="17">
+  <dxfs count="18">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFF9900"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -1374,25 +1451,25 @@
   </dxfs>
   <tableStyles count="2" defaultTableStyle="TableStylePreset3_Accent1" defaultPivotStyle="PivotStylePreset2_Accent1">
     <tableStyle name="TableStylePreset3_Accent1" pivot="0" count="7" xr9:uid="{59DB682C-5494-4EDE-A608-00C9E5F0F923}">
-      <tableStyleElement type="wholeTable" dxfId="6"/>
-      <tableStyleElement type="headerRow" dxfId="5"/>
-      <tableStyleElement type="totalRow" dxfId="4"/>
-      <tableStyleElement type="firstColumn" dxfId="3"/>
-      <tableStyleElement type="lastColumn" dxfId="2"/>
-      <tableStyleElement type="firstRowStripe" dxfId="1"/>
-      <tableStyleElement type="firstColumnStripe" dxfId="0"/>
+      <tableStyleElement type="wholeTable" dxfId="7"/>
+      <tableStyleElement type="headerRow" dxfId="6"/>
+      <tableStyleElement type="totalRow" dxfId="5"/>
+      <tableStyleElement type="firstColumn" dxfId="4"/>
+      <tableStyleElement type="lastColumn" dxfId="3"/>
+      <tableStyleElement type="firstRowStripe" dxfId="2"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="1"/>
     </tableStyle>
     <tableStyle name="PivotStylePreset2_Accent1" table="0" count="10" xr9:uid="{267968C8-6FFD-4C36-ACC1-9EA1FD1885CA}">
-      <tableStyleElement type="headerRow" dxfId="16"/>
-      <tableStyleElement type="totalRow" dxfId="15"/>
-      <tableStyleElement type="firstRowStripe" dxfId="14"/>
-      <tableStyleElement type="firstColumnStripe" dxfId="13"/>
-      <tableStyleElement type="firstSubtotalRow" dxfId="12"/>
-      <tableStyleElement type="secondSubtotalRow" dxfId="11"/>
-      <tableStyleElement type="firstRowSubheading" dxfId="10"/>
-      <tableStyleElement type="secondRowSubheading" dxfId="9"/>
-      <tableStyleElement type="pageFieldLabels" dxfId="8"/>
-      <tableStyleElement type="pageFieldValues" dxfId="7"/>
+      <tableStyleElement type="headerRow" dxfId="17"/>
+      <tableStyleElement type="totalRow" dxfId="16"/>
+      <tableStyleElement type="firstRowStripe" dxfId="15"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="14"/>
+      <tableStyleElement type="firstSubtotalRow" dxfId="13"/>
+      <tableStyleElement type="secondSubtotalRow" dxfId="12"/>
+      <tableStyleElement type="firstRowSubheading" dxfId="11"/>
+      <tableStyleElement type="secondRowSubheading" dxfId="10"/>
+      <tableStyleElement type="pageFieldLabels" dxfId="9"/>
+      <tableStyleElement type="pageFieldValues" dxfId="8"/>
     </tableStyle>
   </tableStyles>
   <extLst>
@@ -1672,477 +1749,713 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:BX3"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8" outlineLevelRow="2"/>
+  <dimension ref="A1:BX4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8" outlineLevelRow="3"/>
   <cols>
-    <col min="1" max="1" width="5.125" style="1" customWidth="1"/>
-    <col min="2" max="2" width="6.44230769230769" style="1" customWidth="1"/>
-    <col min="3" max="3" width="6.625" style="1" customWidth="1"/>
-    <col min="4" max="4" width="9.22115384615385" style="1" customWidth="1"/>
-    <col min="5" max="5" width="9" style="2" customWidth="1"/>
-    <col min="6" max="6" width="14.7788461538462" style="1" customWidth="1"/>
-    <col min="7" max="7" width="9.66346153846154" style="1" customWidth="1"/>
-    <col min="8" max="8" width="8.38461538461539" style="1" customWidth="1"/>
-    <col min="9" max="9" width="4.88461538461539" style="1" customWidth="1"/>
-    <col min="10" max="10" width="8" style="1" customWidth="1"/>
-    <col min="11" max="11" width="10.7788461538462" style="1" customWidth="1"/>
-    <col min="12" max="12" width="8.625" style="1" customWidth="1"/>
-    <col min="13" max="13" width="10.7788461538462" style="3" customWidth="1"/>
-    <col min="14" max="14" width="8.625" style="4" customWidth="1"/>
-    <col min="15" max="15" width="8.625" style="1" customWidth="1"/>
-    <col min="16" max="16" width="9.66346153846154" style="1" customWidth="1"/>
-    <col min="17" max="17" width="8.625" style="5" customWidth="1"/>
-    <col min="18" max="18" width="10.7788461538462" style="1" customWidth="1"/>
-    <col min="19" max="19" width="7.5" style="1" customWidth="1"/>
-    <col min="20" max="20" width="6.625" style="1" customWidth="1"/>
-    <col min="21" max="21" width="9.66346153846154" style="1" customWidth="1"/>
-    <col min="22" max="22" width="7.125" style="1" customWidth="1"/>
-    <col min="23" max="23" width="9.66346153846154" style="3" customWidth="1"/>
-    <col min="24" max="24" width="7.5" style="1" customWidth="1"/>
-    <col min="25" max="25" width="7.88461538461539" style="5" customWidth="1"/>
-    <col min="26" max="26" width="8.66346153846154" style="3" customWidth="1"/>
-    <col min="27" max="27" width="7.5" style="1" customWidth="1"/>
-    <col min="28" max="28" width="9.38461538461539" style="1" customWidth="1"/>
-    <col min="29" max="29" width="8.66346153846154" style="1" customWidth="1"/>
-    <col min="30" max="33" width="6.25" style="1" customWidth="1"/>
-    <col min="34" max="34" width="7.125" style="1" customWidth="1"/>
-    <col min="35" max="35" width="8.66346153846154" style="1" customWidth="1"/>
-    <col min="36" max="36" width="7.125" style="1" customWidth="1"/>
-    <col min="37" max="43" width="9.66346153846154" style="1" customWidth="1"/>
-    <col min="44" max="45" width="5.75" style="1" customWidth="1"/>
-    <col min="46" max="46" width="6.75" style="1" customWidth="1"/>
-    <col min="47" max="47" width="5.75" style="1" customWidth="1"/>
-    <col min="48" max="48" width="7.89423076923077" style="1" customWidth="1"/>
-    <col min="49" max="49" width="5.38461538461539" style="1" customWidth="1"/>
-    <col min="50" max="50" width="6.625" style="1" customWidth="1"/>
-    <col min="51" max="51" width="6.38461538461539" style="1" customWidth="1"/>
-    <col min="52" max="53" width="6.625" style="1" customWidth="1"/>
-    <col min="54" max="54" width="5.25" style="1" customWidth="1"/>
-    <col min="55" max="55" width="6.625" style="1" customWidth="1"/>
-    <col min="56" max="61" width="5.625" style="1" customWidth="1"/>
-    <col min="62" max="63" width="7.625" style="4" customWidth="1"/>
-    <col min="64" max="65" width="9.38461538461539" style="1" customWidth="1"/>
-    <col min="66" max="66" width="12.8846153846154" style="1" customWidth="1"/>
-    <col min="67" max="72" width="10.625" style="3" customWidth="1"/>
-    <col min="73" max="73" width="6.88461538461539" style="6" customWidth="1"/>
-    <col min="74" max="74" width="10.625" style="3" customWidth="1"/>
-    <col min="75" max="75" width="11.25" style="3" customWidth="1"/>
-    <col min="76" max="76" width="15.3846153846154" style="4" customWidth="1"/>
+    <col min="1" max="1" width="5.125" style="2" customWidth="1"/>
+    <col min="2" max="2" width="6.44230769230769" style="2" customWidth="1"/>
+    <col min="3" max="3" width="6.625" style="2" customWidth="1"/>
+    <col min="4" max="4" width="9.22115384615385" style="2" customWidth="1"/>
+    <col min="5" max="5" width="9" style="3" customWidth="1"/>
+    <col min="6" max="6" width="14.7788461538462" style="2" customWidth="1"/>
+    <col min="7" max="7" width="9.66346153846154" style="2" customWidth="1"/>
+    <col min="8" max="8" width="8.38461538461539" style="2" customWidth="1"/>
+    <col min="9" max="9" width="4.88461538461539" style="2" customWidth="1"/>
+    <col min="10" max="10" width="8" style="2" customWidth="1"/>
+    <col min="11" max="11" width="10.7788461538462" style="2" customWidth="1"/>
+    <col min="12" max="12" width="8.625" style="2" customWidth="1"/>
+    <col min="13" max="13" width="10.7788461538462" style="4" customWidth="1"/>
+    <col min="14" max="14" width="8.625" style="5" customWidth="1"/>
+    <col min="15" max="15" width="8.625" style="2" customWidth="1"/>
+    <col min="16" max="16" width="9.66346153846154" style="2" customWidth="1"/>
+    <col min="17" max="17" width="8.625" style="6" customWidth="1"/>
+    <col min="18" max="18" width="10.7788461538462" style="2" customWidth="1"/>
+    <col min="19" max="19" width="7.5" style="2" customWidth="1"/>
+    <col min="20" max="20" width="6.625" style="2" customWidth="1"/>
+    <col min="21" max="21" width="9.66346153846154" style="2" customWidth="1"/>
+    <col min="22" max="22" width="7.125" style="2" customWidth="1"/>
+    <col min="23" max="23" width="9.66346153846154" style="4" customWidth="1"/>
+    <col min="24" max="24" width="7.5" style="2" customWidth="1"/>
+    <col min="25" max="25" width="7.88461538461539" style="6" customWidth="1"/>
+    <col min="26" max="26" width="8.66346153846154" style="4" customWidth="1"/>
+    <col min="27" max="27" width="7.5" style="2" customWidth="1"/>
+    <col min="28" max="28" width="9.38461538461539" style="2" customWidth="1"/>
+    <col min="29" max="29" width="8.66346153846154" style="2" customWidth="1"/>
+    <col min="30" max="33" width="6.25" style="2" customWidth="1"/>
+    <col min="34" max="34" width="7.125" style="2" customWidth="1"/>
+    <col min="35" max="35" width="8.66346153846154" style="2" customWidth="1"/>
+    <col min="36" max="36" width="7.125" style="2" customWidth="1"/>
+    <col min="37" max="43" width="9.66346153846154" style="2" customWidth="1"/>
+    <col min="44" max="45" width="5.75" style="2" customWidth="1"/>
+    <col min="46" max="46" width="6.75" style="2" customWidth="1"/>
+    <col min="47" max="47" width="5.75" style="2" customWidth="1"/>
+    <col min="48" max="48" width="7.89423076923077" style="2" customWidth="1"/>
+    <col min="49" max="49" width="5.38461538461539" style="2" customWidth="1"/>
+    <col min="50" max="50" width="6.625" style="2" customWidth="1"/>
+    <col min="51" max="51" width="6.38461538461539" style="2" customWidth="1"/>
+    <col min="52" max="53" width="6.625" style="2" customWidth="1"/>
+    <col min="54" max="54" width="5.25" style="2" customWidth="1"/>
+    <col min="55" max="55" width="6.625" style="2" customWidth="1"/>
+    <col min="56" max="61" width="5.625" style="2" customWidth="1"/>
+    <col min="62" max="63" width="7.625" style="5" customWidth="1"/>
+    <col min="64" max="65" width="9.38461538461539" style="2" customWidth="1"/>
+    <col min="66" max="66" width="12.8846153846154" style="2" customWidth="1"/>
+    <col min="67" max="72" width="10.625" style="4" customWidth="1"/>
+    <col min="73" max="73" width="6.88461538461539" style="7" customWidth="1"/>
+    <col min="74" max="74" width="10.625" style="4" customWidth="1"/>
+    <col min="75" max="75" width="11.25" style="4" customWidth="1"/>
+    <col min="76" max="76" width="15.3846153846154" style="5" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="1" ht="42" customHeight="1" spans="1:76">
-      <c r="A1" s="7" t="s">
+      <c r="A1" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="7"/>
-      <c r="C1" s="7"/>
-      <c r="D1" s="7"/>
-      <c r="E1" s="7"/>
-      <c r="F1" s="7"/>
-      <c r="G1" s="7"/>
-      <c r="H1" s="7"/>
-      <c r="I1" s="7"/>
-      <c r="J1" s="7"/>
-      <c r="K1" s="7"/>
-      <c r="L1" s="7"/>
-      <c r="M1" s="17"/>
-      <c r="N1" s="7"/>
-      <c r="O1" s="7"/>
-      <c r="P1" s="7"/>
-      <c r="Q1" s="7"/>
-      <c r="R1" s="7"/>
-      <c r="S1" s="7"/>
-      <c r="T1" s="7"/>
-      <c r="U1" s="7"/>
-      <c r="V1" s="7"/>
-      <c r="W1" s="17"/>
-      <c r="X1" s="7"/>
-      <c r="Y1" s="7"/>
-      <c r="Z1" s="17"/>
-      <c r="AA1" s="7"/>
-      <c r="AB1" s="7"/>
-      <c r="AC1" s="7"/>
-      <c r="AD1" s="7"/>
-      <c r="AE1" s="7"/>
-      <c r="AF1" s="7"/>
-      <c r="AG1" s="7"/>
-      <c r="AH1" s="7"/>
-      <c r="AI1" s="7"/>
-      <c r="AJ1" s="7"/>
-      <c r="AK1" s="7"/>
-      <c r="AL1" s="7"/>
-      <c r="AM1" s="7"/>
-      <c r="AN1" s="7"/>
-      <c r="AO1" s="7"/>
-      <c r="AP1" s="7"/>
-      <c r="AQ1" s="7"/>
-      <c r="AR1" s="7"/>
-      <c r="AS1" s="7"/>
-      <c r="AT1" s="7"/>
-      <c r="AU1" s="7"/>
-      <c r="AV1" s="7"/>
-      <c r="AW1" s="7"/>
-      <c r="AX1" s="7"/>
-      <c r="AY1" s="7"/>
-      <c r="AZ1" s="7"/>
-      <c r="BA1" s="7"/>
-      <c r="BB1" s="7"/>
-      <c r="BC1" s="7"/>
-      <c r="BD1" s="7"/>
-      <c r="BE1" s="7"/>
-      <c r="BF1" s="7"/>
-      <c r="BG1" s="7"/>
-      <c r="BH1" s="7"/>
-      <c r="BI1" s="7"/>
-      <c r="BJ1" s="7"/>
-      <c r="BK1" s="7"/>
-      <c r="BL1" s="7"/>
-      <c r="BM1" s="7"/>
-      <c r="BN1" s="7"/>
-      <c r="BO1" s="17"/>
-      <c r="BP1" s="17"/>
-      <c r="BQ1" s="17"/>
-      <c r="BR1" s="17"/>
-      <c r="BS1" s="17"/>
-      <c r="BT1" s="17"/>
-      <c r="BU1" s="17"/>
-      <c r="BV1" s="17"/>
-      <c r="BW1" s="17"/>
-      <c r="BX1" s="7"/>
+      <c r="B1" s="8"/>
+      <c r="C1" s="8"/>
+      <c r="D1" s="8"/>
+      <c r="E1" s="8"/>
+      <c r="F1" s="8"/>
+      <c r="G1" s="8"/>
+      <c r="H1" s="8"/>
+      <c r="I1" s="8"/>
+      <c r="J1" s="8"/>
+      <c r="K1" s="8"/>
+      <c r="L1" s="8"/>
+      <c r="M1" s="24"/>
+      <c r="N1" s="8"/>
+      <c r="O1" s="8"/>
+      <c r="P1" s="8"/>
+      <c r="Q1" s="8"/>
+      <c r="R1" s="8"/>
+      <c r="S1" s="8"/>
+      <c r="T1" s="8"/>
+      <c r="U1" s="8"/>
+      <c r="V1" s="8"/>
+      <c r="W1" s="24"/>
+      <c r="X1" s="8"/>
+      <c r="Y1" s="8"/>
+      <c r="Z1" s="24"/>
+      <c r="AA1" s="8"/>
+      <c r="AB1" s="8"/>
+      <c r="AC1" s="8"/>
+      <c r="AD1" s="8"/>
+      <c r="AE1" s="8"/>
+      <c r="AF1" s="8"/>
+      <c r="AG1" s="8"/>
+      <c r="AH1" s="8"/>
+      <c r="AI1" s="8"/>
+      <c r="AJ1" s="8"/>
+      <c r="AK1" s="8"/>
+      <c r="AL1" s="8"/>
+      <c r="AM1" s="8"/>
+      <c r="AN1" s="8"/>
+      <c r="AO1" s="8"/>
+      <c r="AP1" s="8"/>
+      <c r="AQ1" s="8"/>
+      <c r="AR1" s="8"/>
+      <c r="AS1" s="8"/>
+      <c r="AT1" s="8"/>
+      <c r="AU1" s="8"/>
+      <c r="AV1" s="8"/>
+      <c r="AW1" s="8"/>
+      <c r="AX1" s="8"/>
+      <c r="AY1" s="8"/>
+      <c r="AZ1" s="8"/>
+      <c r="BA1" s="8"/>
+      <c r="BB1" s="8"/>
+      <c r="BC1" s="8"/>
+      <c r="BD1" s="8"/>
+      <c r="BE1" s="8"/>
+      <c r="BF1" s="8"/>
+      <c r="BG1" s="8"/>
+      <c r="BH1" s="8"/>
+      <c r="BI1" s="8"/>
+      <c r="BJ1" s="8"/>
+      <c r="BK1" s="8"/>
+      <c r="BL1" s="8"/>
+      <c r="BM1" s="8"/>
+      <c r="BN1" s="8"/>
+      <c r="BO1" s="24"/>
+      <c r="BP1" s="24"/>
+      <c r="BQ1" s="24"/>
+      <c r="BR1" s="24"/>
+      <c r="BS1" s="24"/>
+      <c r="BT1" s="24"/>
+      <c r="BU1" s="24"/>
+      <c r="BV1" s="24"/>
+      <c r="BW1" s="24"/>
+      <c r="BX1" s="8"/>
     </row>
     <row r="2" customFormat="1" ht="25" customHeight="1" spans="1:76">
-      <c r="A2" s="8" t="s">
+      <c r="A2" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="8" t="s">
+      <c r="B2" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="9" t="s">
+      <c r="C2" s="10" t="s">
         <v>3</v>
       </c>
-      <c r="D2" s="10" t="s">
+      <c r="D2" s="11" t="s">
         <v>4</v>
       </c>
-      <c r="E2" s="10" t="s">
+      <c r="E2" s="11" t="s">
         <v>5</v>
       </c>
-      <c r="F2" s="12" t="s">
+      <c r="F2" s="16" t="s">
         <v>6</v>
       </c>
-      <c r="G2" s="12" t="s">
+      <c r="G2" s="16" t="s">
         <v>7</v>
       </c>
-      <c r="H2" s="12" t="s">
+      <c r="H2" s="16" t="s">
         <v>8</v>
       </c>
-      <c r="I2" s="14" t="s">
+      <c r="I2" s="20" t="s">
         <v>9</v>
       </c>
-      <c r="J2" s="15"/>
-      <c r="K2" s="15"/>
-      <c r="L2" s="15"/>
-      <c r="M2" s="18"/>
-      <c r="N2" s="19" t="s">
+      <c r="J2" s="21"/>
+      <c r="K2" s="21"/>
+      <c r="L2" s="21"/>
+      <c r="M2" s="25"/>
+      <c r="N2" s="26" t="s">
         <v>10</v>
       </c>
-      <c r="O2" s="20"/>
-      <c r="P2" s="20"/>
-      <c r="Q2" s="22"/>
-      <c r="R2" s="20"/>
-      <c r="S2" s="23" t="s">
+      <c r="O2" s="27"/>
+      <c r="P2" s="27"/>
+      <c r="Q2" s="30"/>
+      <c r="R2" s="27"/>
+      <c r="S2" s="31" t="s">
         <v>11</v>
       </c>
-      <c r="T2" s="23"/>
-      <c r="U2" s="23"/>
-      <c r="V2" s="23"/>
-      <c r="W2" s="25"/>
-      <c r="X2" s="26" t="s">
+      <c r="T2" s="31"/>
+      <c r="U2" s="31"/>
+      <c r="V2" s="31"/>
+      <c r="W2" s="33"/>
+      <c r="X2" s="34" t="s">
         <v>12</v>
       </c>
-      <c r="Y2" s="9"/>
-      <c r="Z2" s="25"/>
-      <c r="AA2" s="28" t="s">
+      <c r="Y2" s="10"/>
+      <c r="Z2" s="33"/>
+      <c r="AA2" s="36" t="s">
         <v>13</v>
       </c>
-      <c r="AB2" s="28"/>
-      <c r="AC2" s="28"/>
-      <c r="AD2" s="30" t="s">
+      <c r="AB2" s="36"/>
+      <c r="AC2" s="36"/>
+      <c r="AD2" s="39" t="s">
         <v>14</v>
       </c>
-      <c r="AE2" s="30"/>
-      <c r="AF2" s="30"/>
-      <c r="AG2" s="31" t="s">
+      <c r="AE2" s="39"/>
+      <c r="AF2" s="39"/>
+      <c r="AG2" s="40" t="s">
         <v>15</v>
       </c>
-      <c r="AH2" s="31"/>
-      <c r="AI2" s="31"/>
-      <c r="AJ2" s="31"/>
-      <c r="AK2" s="32"/>
-      <c r="AL2" s="33" t="s">
+      <c r="AH2" s="40"/>
+      <c r="AI2" s="40"/>
+      <c r="AJ2" s="40"/>
+      <c r="AK2" s="41"/>
+      <c r="AL2" s="42" t="s">
         <v>16</v>
       </c>
-      <c r="AM2" s="33"/>
-      <c r="AN2" s="33"/>
-      <c r="AO2" s="33"/>
-      <c r="AP2" s="35"/>
-      <c r="AQ2" s="36" t="s">
+      <c r="AM2" s="42"/>
+      <c r="AN2" s="42"/>
+      <c r="AO2" s="42"/>
+      <c r="AP2" s="46"/>
+      <c r="AQ2" s="47" t="s">
         <v>17</v>
       </c>
-      <c r="AR2" s="37" t="s">
+      <c r="AR2" s="48" t="s">
         <v>18</v>
       </c>
-      <c r="AS2" s="39"/>
-      <c r="AT2" s="39"/>
-      <c r="AU2" s="39"/>
-      <c r="AV2" s="39"/>
-      <c r="AW2" s="40" t="s">
+      <c r="AS2" s="51"/>
+      <c r="AT2" s="51"/>
+      <c r="AU2" s="51"/>
+      <c r="AV2" s="51"/>
+      <c r="AW2" s="52" t="s">
         <v>19</v>
       </c>
-      <c r="AX2" s="41"/>
-      <c r="AY2" s="41"/>
-      <c r="AZ2" s="41"/>
-      <c r="BA2" s="43"/>
-      <c r="BB2" s="27" t="s">
+      <c r="AX2" s="53"/>
+      <c r="AY2" s="53"/>
+      <c r="AZ2" s="53"/>
+      <c r="BA2" s="55"/>
+      <c r="BB2" s="35" t="s">
         <v>20</v>
       </c>
-      <c r="BC2" s="44"/>
-      <c r="BD2" s="45"/>
-      <c r="BE2" s="40" t="s">
+      <c r="BC2" s="56"/>
+      <c r="BD2" s="57"/>
+      <c r="BE2" s="52" t="s">
         <v>21</v>
       </c>
-      <c r="BF2" s="41"/>
-      <c r="BG2" s="41"/>
-      <c r="BH2" s="41"/>
-      <c r="BI2" s="43"/>
-      <c r="BJ2" s="8" t="s">
+      <c r="BF2" s="53"/>
+      <c r="BG2" s="53"/>
+      <c r="BH2" s="53"/>
+      <c r="BI2" s="55"/>
+      <c r="BJ2" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="BK2" s="8" t="s">
+      <c r="BK2" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="BL2" s="8" t="s">
+      <c r="BL2" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="BM2" s="8" t="s">
+      <c r="BM2" s="9" t="s">
         <v>25</v>
       </c>
-      <c r="BN2" s="8" t="s">
+      <c r="BN2" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="BO2" s="45" t="s">
+      <c r="BO2" s="57" t="s">
         <v>27</v>
       </c>
-      <c r="BP2" s="46" t="s">
+      <c r="BP2" s="58" t="s">
         <v>28</v>
       </c>
-      <c r="BQ2" s="46" t="s">
+      <c r="BQ2" s="58" t="s">
         <v>29</v>
       </c>
-      <c r="BR2" s="45" t="s">
+      <c r="BR2" s="57" t="s">
         <v>30</v>
       </c>
-      <c r="BS2" s="45" t="s">
+      <c r="BS2" s="57" t="s">
         <v>31</v>
       </c>
-      <c r="BT2" s="46" t="s">
+      <c r="BT2" s="58" t="s">
         <v>32</v>
       </c>
-      <c r="BU2" s="48" t="s">
+      <c r="BU2" s="61" t="s">
         <v>33</v>
       </c>
-      <c r="BV2" s="46" t="s">
+      <c r="BV2" s="58" t="s">
         <v>34</v>
       </c>
-      <c r="BW2" s="46" t="s">
+      <c r="BW2" s="58" t="s">
         <v>35</v>
       </c>
-      <c r="BX2" s="9" t="s">
+      <c r="BX2" s="10" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="3" customFormat="1" ht="41" customHeight="1" spans="1:76">
-      <c r="A3" s="11"/>
-      <c r="B3" s="11"/>
-      <c r="C3" s="9"/>
-      <c r="D3" s="10"/>
-      <c r="E3" s="10"/>
-      <c r="F3" s="13"/>
-      <c r="G3" s="13"/>
-      <c r="H3" s="13"/>
-      <c r="I3" s="16" t="s">
+      <c r="A3" s="12"/>
+      <c r="B3" s="12"/>
+      <c r="C3" s="10"/>
+      <c r="D3" s="11"/>
+      <c r="E3" s="11"/>
+      <c r="F3" s="17"/>
+      <c r="G3" s="17"/>
+      <c r="H3" s="17"/>
+      <c r="I3" s="22" t="s">
         <v>37</v>
       </c>
-      <c r="J3" s="16" t="s">
+      <c r="J3" s="22" t="s">
         <v>38</v>
       </c>
-      <c r="K3" s="16" t="s">
+      <c r="K3" s="22" t="s">
         <v>39</v>
       </c>
-      <c r="L3" s="16" t="s">
+      <c r="L3" s="22" t="s">
         <v>40</v>
       </c>
-      <c r="M3" s="16" t="s">
+      <c r="M3" s="22" t="s">
         <v>41</v>
       </c>
-      <c r="N3" s="21" t="s">
+      <c r="N3" s="28" t="s">
         <v>37</v>
       </c>
-      <c r="O3" s="21" t="s">
+      <c r="O3" s="28" t="s">
         <v>42</v>
       </c>
-      <c r="P3" s="21" t="s">
+      <c r="P3" s="28" t="s">
         <v>39</v>
       </c>
-      <c r="Q3" s="21" t="s">
+      <c r="Q3" s="28" t="s">
         <v>43</v>
       </c>
-      <c r="R3" s="19" t="s">
+      <c r="R3" s="26" t="s">
         <v>41</v>
       </c>
-      <c r="S3" s="24" t="s">
+      <c r="S3" s="32" t="s">
         <v>37</v>
       </c>
-      <c r="T3" s="24" t="s">
+      <c r="T3" s="32" t="s">
         <v>44</v>
       </c>
-      <c r="U3" s="24" t="s">
+      <c r="U3" s="32" t="s">
         <v>45</v>
       </c>
-      <c r="V3" s="24" t="s">
+      <c r="V3" s="32" t="s">
         <v>46</v>
       </c>
-      <c r="W3" s="24" t="s">
+      <c r="W3" s="32" t="s">
         <v>41</v>
       </c>
-      <c r="X3" s="27" t="s">
+      <c r="X3" s="35" t="s">
         <v>37</v>
       </c>
-      <c r="Y3" s="27" t="s">
+      <c r="Y3" s="35" t="s">
         <v>47</v>
       </c>
-      <c r="Z3" s="27" t="s">
+      <c r="Z3" s="35" t="s">
         <v>48</v>
       </c>
-      <c r="AA3" s="29" t="s">
+      <c r="AA3" s="37" t="s">
         <v>37</v>
       </c>
-      <c r="AB3" s="29" t="s">
+      <c r="AB3" s="37" t="s">
         <v>49</v>
       </c>
-      <c r="AC3" s="29" t="s">
+      <c r="AC3" s="37" t="s">
         <v>48</v>
       </c>
-      <c r="AD3" s="29" t="s">
+      <c r="AD3" s="37" t="s">
         <v>37</v>
       </c>
-      <c r="AE3" s="29" t="s">
+      <c r="AE3" s="37" t="s">
         <v>50</v>
       </c>
-      <c r="AF3" s="29" t="s">
+      <c r="AF3" s="37" t="s">
         <v>48</v>
       </c>
-      <c r="AG3" s="24" t="s">
+      <c r="AG3" s="32" t="s">
         <v>37</v>
       </c>
-      <c r="AH3" s="24" t="s">
+      <c r="AH3" s="32" t="s">
         <v>51</v>
       </c>
-      <c r="AI3" s="24" t="s">
+      <c r="AI3" s="32" t="s">
         <v>45</v>
       </c>
-      <c r="AJ3" s="24" t="s">
+      <c r="AJ3" s="32" t="s">
         <v>52</v>
       </c>
-      <c r="AK3" s="24" t="s">
+      <c r="AK3" s="32" t="s">
         <v>41</v>
       </c>
-      <c r="AL3" s="34" t="s">
+      <c r="AL3" s="43" t="s">
         <v>37</v>
       </c>
-      <c r="AM3" s="34" t="s">
+      <c r="AM3" s="43" t="s">
         <v>53</v>
       </c>
-      <c r="AN3" s="34" t="s">
+      <c r="AN3" s="43" t="s">
         <v>39</v>
       </c>
-      <c r="AO3" s="34" t="s">
+      <c r="AO3" s="43" t="s">
         <v>54</v>
       </c>
-      <c r="AP3" s="34" t="s">
+      <c r="AP3" s="43" t="s">
         <v>41</v>
       </c>
-      <c r="AQ3" s="36" t="s">
+      <c r="AQ3" s="47" t="s">
         <v>41</v>
       </c>
-      <c r="AR3" s="38" t="s">
+      <c r="AR3" s="49" t="s">
         <v>37</v>
       </c>
-      <c r="AS3" s="38" t="s">
+      <c r="AS3" s="49" t="s">
         <v>55</v>
       </c>
-      <c r="AT3" s="38" t="s">
+      <c r="AT3" s="49" t="s">
         <v>56</v>
       </c>
-      <c r="AU3" s="38" t="s">
+      <c r="AU3" s="49" t="s">
         <v>57</v>
       </c>
-      <c r="AV3" s="38" t="s">
+      <c r="AV3" s="49" t="s">
         <v>56</v>
       </c>
-      <c r="AW3" s="42" t="s">
+      <c r="AW3" s="54" t="s">
         <v>37</v>
       </c>
-      <c r="AX3" s="42" t="s">
+      <c r="AX3" s="54" t="s">
         <v>55</v>
       </c>
-      <c r="AY3" s="42" t="s">
+      <c r="AY3" s="54" t="s">
         <v>56</v>
       </c>
-      <c r="AZ3" s="42" t="s">
+      <c r="AZ3" s="54" t="s">
         <v>57</v>
       </c>
-      <c r="BA3" s="42" t="s">
+      <c r="BA3" s="54" t="s">
         <v>56</v>
       </c>
-      <c r="BB3" s="27" t="s">
+      <c r="BB3" s="35" t="s">
         <v>37</v>
       </c>
-      <c r="BC3" s="27" t="s">
+      <c r="BC3" s="35" t="s">
         <v>57</v>
       </c>
-      <c r="BD3" s="27" t="s">
+      <c r="BD3" s="35" t="s">
         <v>48</v>
       </c>
-      <c r="BE3" s="42" t="s">
+      <c r="BE3" s="54" t="s">
         <v>37</v>
       </c>
-      <c r="BF3" s="42" t="s">
+      <c r="BF3" s="54" t="s">
         <v>55</v>
       </c>
-      <c r="BG3" s="42" t="s">
+      <c r="BG3" s="54" t="s">
         <v>56</v>
       </c>
-      <c r="BH3" s="42" t="s">
+      <c r="BH3" s="54" t="s">
         <v>57</v>
       </c>
-      <c r="BI3" s="42" t="s">
+      <c r="BI3" s="54" t="s">
         <v>56</v>
       </c>
-      <c r="BJ3" s="13"/>
-      <c r="BK3" s="13"/>
-      <c r="BL3" s="13"/>
-      <c r="BM3" s="13"/>
-      <c r="BN3" s="11"/>
-      <c r="BO3" s="45"/>
-      <c r="BP3" s="47"/>
-      <c r="BQ3" s="47"/>
-      <c r="BR3" s="45"/>
-      <c r="BS3" s="45"/>
-      <c r="BT3" s="47"/>
-      <c r="BU3" s="49"/>
-      <c r="BV3" s="47"/>
-      <c r="BW3" s="47"/>
-      <c r="BX3" s="9"/>
+      <c r="BJ3" s="17"/>
+      <c r="BK3" s="17"/>
+      <c r="BL3" s="17"/>
+      <c r="BM3" s="17"/>
+      <c r="BN3" s="12"/>
+      <c r="BO3" s="57"/>
+      <c r="BP3" s="59"/>
+      <c r="BQ3" s="59"/>
+      <c r="BR3" s="57"/>
+      <c r="BS3" s="57"/>
+      <c r="BT3" s="59"/>
+      <c r="BU3" s="62"/>
+      <c r="BV3" s="59"/>
+      <c r="BW3" s="59"/>
+      <c r="BX3" s="10"/>
+    </row>
+    <row r="4" s="1" customFormat="1" ht="18" customHeight="1" spans="1:76">
+      <c r="A4" s="13">
+        <v>1</v>
+      </c>
+      <c r="B4" s="14" t="s">
+        <v>58</v>
+      </c>
+      <c r="C4" s="15" t="s">
+        <v>59</v>
+      </c>
+      <c r="D4" s="15" t="s">
+        <v>60</v>
+      </c>
+      <c r="E4" s="18" t="s">
+        <v>61</v>
+      </c>
+      <c r="F4" s="19" t="s">
+        <v>62</v>
+      </c>
+      <c r="G4" s="13">
+        <v>202509</v>
+      </c>
+      <c r="H4" s="15">
+        <v>202605</v>
+      </c>
+      <c r="I4" s="15">
+        <v>1234</v>
+      </c>
+      <c r="J4" s="23">
+        <v>0.08</v>
+      </c>
+      <c r="K4" s="15">
+        <f>ROUND(I4*J4,2)</f>
+        <v>98.72</v>
+      </c>
+      <c r="L4" s="23">
+        <v>0.16</v>
+      </c>
+      <c r="M4" s="15">
+        <f>ROUND(I4*L4,2)</f>
+        <v>197.44</v>
+      </c>
+      <c r="N4" s="15">
+        <v>1234</v>
+      </c>
+      <c r="O4" s="29">
+        <v>0.02</v>
+      </c>
+      <c r="P4" s="15">
+        <f>ROUND(N4*O4,2)</f>
+        <v>24.68</v>
+      </c>
+      <c r="Q4" s="23">
+        <v>0.068</v>
+      </c>
+      <c r="R4" s="15">
+        <f>ROUND(N4*Q4,2)</f>
+        <v>83.91</v>
+      </c>
+      <c r="S4" s="15">
+        <v>1234</v>
+      </c>
+      <c r="T4" s="23">
+        <v>0.005</v>
+      </c>
+      <c r="U4" s="15">
+        <f>ROUND(S4*T4,2)</f>
+        <v>6.17</v>
+      </c>
+      <c r="V4" s="23">
+        <v>0.005</v>
+      </c>
+      <c r="W4" s="15">
+        <f>ROUND(S4*V4,2)</f>
+        <v>6.17</v>
+      </c>
+      <c r="X4" s="15">
+        <v>1234</v>
+      </c>
+      <c r="Y4" s="23">
+        <v>0.0032</v>
+      </c>
+      <c r="Z4" s="15">
+        <f>ROUND(X4*Y4,2)</f>
+        <v>3.95</v>
+      </c>
+      <c r="AA4" s="15">
+        <v>1234</v>
+      </c>
+      <c r="AB4" s="38">
+        <v>0.0012</v>
+      </c>
+      <c r="AC4" s="15">
+        <f>ROUND(AA4*AB4,2)</f>
+        <v>1.48</v>
+      </c>
+      <c r="AD4" s="15">
+        <v>1234</v>
+      </c>
+      <c r="AE4" s="23">
+        <v>0.002</v>
+      </c>
+      <c r="AF4" s="15">
+        <f>ROUND(AD4*AE4,2)</f>
+        <v>2.47</v>
+      </c>
+      <c r="AG4" s="15">
+        <v>1234</v>
+      </c>
+      <c r="AH4" s="23">
+        <v>0.002</v>
+      </c>
+      <c r="AI4" s="15">
+        <f>ROUND(AG4*AH4,2)</f>
+        <v>2.47</v>
+      </c>
+      <c r="AJ4" s="23">
+        <v>0.003</v>
+      </c>
+      <c r="AK4" s="15">
+        <f>ROUND(AG4*AJ4,2)</f>
+        <v>3.7</v>
+      </c>
+      <c r="AL4" s="44">
+        <v>1234</v>
+      </c>
+      <c r="AM4" s="45">
+        <v>0.05</v>
+      </c>
+      <c r="AN4" s="44">
+        <f>ROUND(AL4*AM4,2)</f>
+        <v>61.7</v>
+      </c>
+      <c r="AO4" s="45">
+        <v>0.05</v>
+      </c>
+      <c r="AP4" s="44">
+        <f>ROUND(AL4*AO4,2)</f>
+        <v>61.7</v>
+      </c>
+      <c r="AQ4" s="50">
+        <v>0</v>
+      </c>
+      <c r="AR4" s="15">
+        <v>1234</v>
+      </c>
+      <c r="AS4" s="23">
+        <v>0.02</v>
+      </c>
+      <c r="AT4" s="15">
+        <v>12.16</v>
+      </c>
+      <c r="AU4" s="23">
+        <v>0.068</v>
+      </c>
+      <c r="AV4" s="15">
+        <v>24.32</v>
+      </c>
+      <c r="AW4" s="15">
+        <v>1234</v>
+      </c>
+      <c r="AX4" s="23">
+        <v>0.005</v>
+      </c>
+      <c r="AY4" s="15">
+        <v>0.76</v>
+      </c>
+      <c r="AZ4" s="23">
+        <v>0.005</v>
+      </c>
+      <c r="BA4" s="15">
+        <v>0.76</v>
+      </c>
+      <c r="BB4" s="15">
+        <v>1234</v>
+      </c>
+      <c r="BC4" s="23">
+        <v>0.0032</v>
+      </c>
+      <c r="BD4" s="15">
+        <v>0.5</v>
+      </c>
+      <c r="BE4" s="15">
+        <v>1234</v>
+      </c>
+      <c r="BF4" s="23">
+        <v>0.005</v>
+      </c>
+      <c r="BG4" s="15">
+        <v>0.76</v>
+      </c>
+      <c r="BH4" s="23">
+        <v>0.005</v>
+      </c>
+      <c r="BI4" s="15">
+        <v>0.76</v>
+      </c>
+      <c r="BJ4" s="18">
+        <f>AT4+AY4</f>
+        <v>12.92</v>
+      </c>
+      <c r="BK4" s="18">
+        <f>AV4+BA4+BD4+BI4</f>
+        <v>26.34</v>
+      </c>
+      <c r="BL4" s="18"/>
+      <c r="BM4" s="18"/>
+      <c r="BN4" s="18"/>
+      <c r="BO4" s="60">
+        <f>K4+P4+U4+AI4+BJ4</f>
+        <v>144.96</v>
+      </c>
+      <c r="BP4" s="60">
+        <f>M4+R4+W4+Z4+AK4+BK4+AC4+BN4</f>
+        <v>322.99</v>
+      </c>
+      <c r="BQ4" s="60">
+        <f>BO4+BP4</f>
+        <v>467.95</v>
+      </c>
+      <c r="BR4" s="60"/>
+      <c r="BS4" s="60"/>
+      <c r="BT4" s="60"/>
+      <c r="BU4" s="63">
+        <v>0</v>
+      </c>
+      <c r="BV4" s="60">
+        <f>ROUND((BQ4+BU4)*6.72%,2)</f>
+        <v>31.45</v>
+      </c>
+      <c r="BW4" s="60">
+        <f>BQ4+BU4+BV4</f>
+        <v>499.4</v>
+      </c>
+      <c r="BX4" s="13"/>
     </row>
   </sheetData>
   <mergeCells count="36">
@@ -2183,6 +2496,9 @@
     <mergeCell ref="BW2:BW3"/>
     <mergeCell ref="BX2:BX3"/>
   </mergeCells>
+  <conditionalFormatting sqref="F4">
+    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
+  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
   <headerFooter/>
